--- a/out/Attention-MambaAMT_repeat_2_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6958951686397941</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6958951686397941</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.668078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6958951686397941</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.268078547550069</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.268078547550069</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6958951686397941</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.268078547550069</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.268078547550069</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6958951686397941</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.295895168639794</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.668078547550069</v>
+        <v>2.571991106271275</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.295895168639794</v>
+        <v>3.171991106271274</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001568374009518884</v>
+        <v>-6.876286782044917e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.06752963124648992</v>
+        <v>0.02960718735306106</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.3824533321832731</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1352394812245243</v>
+        <v>0.05929360343215056</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2609018513935854</v>
+        <v>0.1143882226024582</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5896878996927464</v>
+        <v>0.2585400172103611</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.08025487202923968</v>
+        <v>0.03518696751171627</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4889648749426005</v>
+        <v>0.2143792669448496</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01628431052253209</v>
+        <v>0.007139425087827127</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4411524670669308</v>
+        <v>0.1934163753199086</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01410329442246654</v>
+        <v>0.006181444331764272</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4530563292791617</v>
+        <v>0.1986335244703523</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006892974688732529</v>
+        <v>0.003019076583653798</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4527229488624197</v>
+        <v>0.1984845533292524</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003287081527925175</v>
+        <v>0.001438250679991553</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4523968289243241</v>
+        <v>0.1983387562335834</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001366733940292212</v>
+        <v>0.0005962470192839242</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4518387667429389</v>
+        <v>0.1980912310197968</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0009456992757121823</v>
+        <v>0.0004117026046141059</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4523621893184872</v>
+        <v>0.1983180600305777</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003918808065772535</v>
+        <v>0.0001689574963893806</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4521992181818257</v>
+        <v>0.1982436918974516</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002007968562210176</v>
+        <v>8.520316749947203e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4522085174647165</v>
+        <v>0.1982449833535606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.582906931333581e-05</v>
+        <v>3.069075787861581e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4521591365822372</v>
+        <v>0.1982203866002581</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.909276112286344e-05</v>
+        <v>1.446953088542022e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4521614028869504</v>
+        <v>0.1982185950984431</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.645752582315463e-05</v>
+        <v>4.599419447200756e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4521557406256443</v>
+        <v>0.1982133023896641</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.123686696358992e-06</v>
+        <v>-7.373950752172664e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4521494736183561</v>
+        <v>0.1982077504535345</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.882814673064221e-07</v>
+        <v>-3.155312586922569e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4521430273050983</v>
+        <v>0.1982021001883813</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.932986608081494e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4521375435682626</v>
+        <v>0.1981968588670804</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.36427134277522e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4521320633436954</v>
+        <v>0.1981915709282299</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4521266560010384</v>
+        <v>0.198186299094179</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.452121734847317</v>
+        <v>0.1981863389496512</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4521217747027892</v>
+        <v>0.1981863788051235</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4521217667316948</v>
+        <v>0.198186370834029</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4521219261535839</v>
+        <v>0.1981865302559181</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.1981864346027847</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4521221812286068</v>
+        <v>0.198186785330941</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4521219341246784</v>
+        <v>0.1981865382270126</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4521218942692061</v>
+        <v>0.1981864983715403</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.1981864346027847</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4521219022403006</v>
+        <v>0.1981865063426348</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.1981864346027847</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4521219341246784</v>
+        <v>0.1981865382270126</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4521220297778121</v>
+        <v>0.1981866338801463</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4521219660090562</v>
+        <v>0.1981865701113904</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4521219261535839</v>
+        <v>0.1981865302559181</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4521219022403006</v>
+        <v>0.1981865063426348</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4521216551363724</v>
+        <v>0.1981862592387067</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4521215754254276</v>
+        <v>0.1981861795277619</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4521216232519944</v>
+        <v>0.1981862273543286</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4521217428184114</v>
+        <v>0.1981863469207457</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4521217268762225</v>
+        <v>0.1981863309785568</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4521217428184114</v>
+        <v>0.1981863469207457</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4521217268762225</v>
+        <v>0.1981863309785568</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4521217826738837</v>
+        <v>0.198186386776218</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4521217826738837</v>
+        <v>0.198186386776218</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4521217826738837</v>
+        <v>0.198186386776218</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4521219341246784</v>
+        <v>0.1981865382270126</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4521221493442289</v>
+        <v>0.1981867534465631</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4521220616621899</v>
+        <v>0.1981866657645241</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4521220138356232</v>
+        <v>0.1981866179379574</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4521220616621899</v>
+        <v>0.1981866657645241</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4521218783270172</v>
+        <v>0.1981864824293514</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4521218862981116</v>
+        <v>0.1981864904004459</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4521218942692061</v>
+        <v>0.1981864983715403</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4521219022403006</v>
+        <v>0.1981865063426348</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4521219022403006</v>
+        <v>0.1981865063426348</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4521219420957728</v>
+        <v>0.1981865461981071</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4521220058645287</v>
+        <v>0.1981866099668629</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4521221174598511</v>
+        <v>0.1981867215621853</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4521221652864178</v>
+        <v>0.1981867693887521</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4521221254309455</v>
+        <v>0.1981867295332798</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4521220536910954</v>
+        <v>0.1981866577934297</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4521221732575122</v>
+        <v>0.1981867773598465</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4521220138356232</v>
+        <v>0.1981866179379574</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4521217826738837</v>
+        <v>0.198186386776218</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.452121734847317</v>
+        <v>0.1981863389496512</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4521217667316948</v>
+        <v>0.198186370834029</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.1981864346027847</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.1981864346027847</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4521217507895059</v>
+        <v>0.1981863548918401</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4521216312230888</v>
+        <v>0.1981862353254231</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4521215913676165</v>
+        <v>0.1981861954699508</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.452121734847317</v>
+        <v>0.1981863389496512</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4521218703559227</v>
+        <v>0.198186474458257</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4521218544137338</v>
+        <v>0.1981864585160681</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.1981864346027847</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4521217906449781</v>
+        <v>0.1981863947473124</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4521216870207502</v>
+        <v>0.1981862911230845</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4521215674543332</v>
+        <v>0.1981861715566674</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4521216870207502</v>
+        <v>0.1981862911230845</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.452121734847317</v>
+        <v>0.1981863389496512</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.1981864346027847</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4521217109340336</v>
+        <v>0.1981863150363679</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.9824533321832731</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4521217189051281</v>
+        <v>0.1981863230074623</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA7" t="n">
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-2.268078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0001568374009518884</v>
+        <v>-0.000168844026491046</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.06752963124648992</v>
+        <v>0.0726992285290488</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1352394812245243</v>
+        <v>0.1455926870488606</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2609018513935854</v>
+        <v>0.2808763944091114</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5896878996927464</v>
+        <v>0.634831944275206</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.08025487202923968</v>
+        <v>0.08639864442054877</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.4889648749426005</v>
+        <v>0.5263982920556597</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.01628431052253209</v>
+        <v>0.0175311342066532</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4411524670669308</v>
+        <v>0.4749257339983203</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01410329442246654</v>
+        <v>0.01518238356900262</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.4530563292791617</v>
+        <v>0.487740702512417</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.006892974688732529</v>
+        <v>0.007421488073144246</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4527229488624197</v>
+        <v>0.4873821792010171</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.003287081527925175</v>
+        <v>0.00353898222531259</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4523968289243241</v>
+        <v>0.4870314905200246</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001366733940292212</v>
+        <v>0.001471395458463858</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4518387667429389</v>
+        <v>0.4864311188171399</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.0009456992757121823</v>
+        <v>0.001018236395774638</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4523621893184872</v>
+        <v>0.4869950745684898</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0003918808065772535</v>
+        <v>0.000422162296689479</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.4521992181818257</v>
+        <v>0.486819922901747</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002007968562210176</v>
+        <v>0.0002168329748875905</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4522085174647165</v>
+        <v>0.4868303364144736</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>7.582906931333581e-05</v>
+        <v>8.212743835073858e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4521591365822372</v>
+        <v>0.4867774972814115</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>3.909276112286344e-05</v>
+        <v>4.252856069087878e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4521614028869504</v>
+        <v>0.4867803297916865</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.645752582315463e-05</v>
+        <v>1.815154101971947e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4521557406256443</v>
+        <v>0.4867746158758903</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>5.123686696358992e-06</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4521494736183561</v>
+        <v>0.4867682507400417</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4521430273050983</v>
+        <v>0.4867617326869341</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4521375435682626</v>
+        <v>0.4867562011235317</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.36427134277522e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-2.268078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4521320633436954</v>
+        <v>0.4867506242663809</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4521266560010384</v>
+        <v>0.4867452169237239</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.452121734847317</v>
+        <v>0.4867402957700026</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4521217747027892</v>
+        <v>0.4867403356254748</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4521217667316948</v>
+        <v>0.4867403276543804</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4521219261535839</v>
+        <v>0.4867404870762695</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.486740391423136</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4521221812286068</v>
+        <v>0.4867407421512923</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4521219341246784</v>
+        <v>0.4867404950473639</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4521218942692061</v>
+        <v>0.4867404551918916</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.6428995442101445</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.486740391423136</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4521219022403006</v>
+        <v>0.4867404631629861</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.486740391423136</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4521219341246784</v>
+        <v>0.4867404950473639</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4521220297778121</v>
+        <v>0.4867405907004976</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4521219660090562</v>
+        <v>0.4867405269317417</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4521219261535839</v>
+        <v>0.4867404870762695</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4521219022403006</v>
+        <v>0.4867404631629861</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4521216551363724</v>
+        <v>0.486740216059058</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4521215754254276</v>
+        <v>0.4867401363481132</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4521216232519944</v>
+        <v>0.4867401841746799</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4521217428184114</v>
+        <v>0.486740303741097</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4521217268762225</v>
+        <v>0.4867402877989081</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4521217428184114</v>
+        <v>0.486740303741097</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4521217268762225</v>
+        <v>0.4867402877989081</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4521217826738837</v>
+        <v>0.4867403435965693</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4521217826738837</v>
+        <v>0.4867403435965693</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4521217826738837</v>
+        <v>0.4867403435965693</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4521219341246784</v>
+        <v>0.4867404950473639</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4521221493442289</v>
+        <v>0.4867407102669145</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4521220616621899</v>
+        <v>0.4867406225848754</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4521220138356232</v>
+        <v>0.4867405747583087</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4521220616621899</v>
+        <v>0.4867406225848754</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4521218783270172</v>
+        <v>0.4867404392497027</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6958951686397941</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4521218862981116</v>
+        <v>0.4867404472207972</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4521218942692061</v>
+        <v>0.4867404551918916</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.668078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4521219022403006</v>
+        <v>0.4867404631629861</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4521219022403006</v>
+        <v>0.4867404631629861</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4521219420957728</v>
+        <v>0.4867405030184584</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4521220058645287</v>
+        <v>0.4867405667872142</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4521221174598511</v>
+        <v>0.4867406783825367</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4521221652864178</v>
+        <v>0.4867407262091034</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4521221254309455</v>
+        <v>0.4867406863536311</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4521220536910954</v>
+        <v>0.486740614613781</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4521221732575122</v>
+        <v>0.4867407341801978</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4521220138356232</v>
+        <v>0.4867405747583087</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4521217826738837</v>
+        <v>0.4867403435965693</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.452121734847317</v>
+        <v>0.4867402957700026</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4521217667316948</v>
+        <v>0.4867403276543804</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.486740391423136</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.486740391423136</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4521217507895059</v>
+        <v>0.4867403117121915</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4521216312230888</v>
+        <v>0.4867401921457744</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.03458016234753856</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4521215913676165</v>
+        <v>0.4867401522903021</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>1.295895168639794</v>
+        <v>0.8428995442101446</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.452121734847317</v>
+        <v>0.4867402957700026</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>1.295895168639794</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4521218703559227</v>
+        <v>0.4867404312786083</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4521218544137338</v>
+        <v>0.4867404153364194</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.486740391423136</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-2.268078547550069</v>
+        <v>-1.389539575462905</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4521217906449781</v>
+        <v>0.4867403515676637</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-2.268078547550069</v>
+        <v>-0.7120598689052218</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4521216870207502</v>
+        <v>0.4867402479434358</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.6958951686397941</v>
+        <v>-0.7120598689052217</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4521215674543332</v>
+        <v>0.4867401283770187</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-2.268078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4521216870207502</v>
+        <v>0.4867402479434358</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.452121734847317</v>
+        <v>0.4867402957700026</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-2.268078547550069</v>
+        <v>0.1654198376524615</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4521218305004505</v>
+        <v>0.486740391423136</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>1.295895168639794</v>
+        <v>-0.5120598689052216</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4521217109340336</v>
+        <v>0.4867402718567191</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.668078547550069</v>
+        <v>-0.17332001562638</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4521217189051281</v>
+        <v>0.4867402798278136</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-MambaAMT_repeat_2_000001.xlsx
+++ b/out/Attention-MambaAMT_repeat_2_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.02425581589341164</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.02058612927794456</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01005652919411659</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.008837539702653885</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.01413554325699806</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.009733553975820541</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.01214981451630592</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.16</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.01924611255526543</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.02155199274420738</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.01872329041361809</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.01119303330779076</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.01988022401928902</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.02988198772072792</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.01504864916205406</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.01980259642004967</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.006689932197332382</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.003852687776088715</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.002242226153612137</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.006538074463605881</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.01213234290480614</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.01072549447417259</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.002723913639783859</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.01334743574261665</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.002061877399682999</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.002292260527610779</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.0008966811001300812</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001531898975372314</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.16</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.01642811670899391</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.01697060093283653</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.3</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.008257433772087097</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.3</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.008885238319635391</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.5120598689052216</v>
+        <v>0.16</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.01773642376065254</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.01566256955265999</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.3</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.008865099400281906</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.01814081147313118</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01302832737565041</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01507779583334923</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.02750055119395256</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.03804929926991463</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.02076775953173637</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.03001061454415321</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.001828592270612717</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.3</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.000168844026491046</v>
+        <v>-7.549743061384651e-05</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.0726992285290488</v>
+        <v>0.03250700163653785</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.01340570673346519</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.1455926870488606</v>
+        <v>0.06510075586587261</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2808763944091114</v>
+        <v>0.1255909113784595</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.001865878701210022</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.634831944275206</v>
+        <v>0.2838603620831945</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.08639864442054877</v>
+        <v>0.03863297737825833</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.01467534527182579</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.5263982920556597</v>
+        <v>0.2353747611161221</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.0175311342066532</v>
+        <v>0.00783871192263551</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.01050508394837379</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.4749257339983203</v>
+        <v>0.2123591837899089</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.01518238356900262</v>
+        <v>0.006787130236714228</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.01005985960364342</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.487740702512417</v>
+        <v>0.2180879121040965</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.007421488073144246</v>
+        <v>0.003315884100197597</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.001440051943063736</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.4873821792010171</v>
+        <v>0.217924827968996</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.00353898222531259</v>
+        <v>0.001579903061546279</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.007106605917215347</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.4870314905200246</v>
+        <v>0.2177652469128931</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.001471395458463858</v>
+        <v>0.0006552583008062353</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.01494976505637169</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.4864311188171399</v>
+        <v>0.2174940408466905</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001018236395774638</v>
+        <v>0.0004526011935854903</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.004857633262872696</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.4869950745684898</v>
+        <v>0.217743387102616</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000422162296689479</v>
+        <v>0.0001857089590046543</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.006291989237070084</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.486819922901747</v>
+        <v>0.2176623513565788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0002168329748875905</v>
+        <v>9.388939844386562e-05</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.01073574647307396</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5120598689052216</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4868303364144736</v>
+        <v>0.2176642463538488</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>8.212743835073858e-05</v>
+        <v>3.383994239731721e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0008985660970211029</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.4867774972814115</v>
+        <v>0.2176377769955543</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>4.252856069087878e-05</v>
+        <v>1.618743066942789e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.00350271537899971</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.4867803297916865</v>
+        <v>0.2176363164230874</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>1.815154101971947e-05</v>
+        <v>5.728762911577315e-06</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.003624524921178818</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6428995442101445</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.4867746158758903</v>
+        <v>0.2176309892779815</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>6.189337927554673e-06</v>
+        <v>-2.045694596194254e-07</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.006267998367547989</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.4867682507400417</v>
+        <v>0.2176253723353827</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>-3.882814673064221e-07</v>
+        <v>-2.694140733653212e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.002820216119289398</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.4867617326869341</v>
+        <v>0.2176196491787541</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.932986608081494e-06</v>
+        <v>-4.173194643232597e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.005852404981851578</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.4867562011235317</v>
+        <v>0.2176144078574532</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-4.04640701416283e-06</v>
+        <v>-4.68213567138761e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.004356883466243744</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.4867506242663809</v>
+        <v>0.2176091199186027</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.004205305129289627</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.4867452169237239</v>
+        <v>0.2176038480845517</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-4.777674021158921e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.004941198974847794</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4867402957700026</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>9.175390005111694e-06</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4867403356254748</v>
+        <v>0.2176039277954963</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.01155875250697136</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4867403276543804</v>
+        <v>0.2176039198244019</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.006684433668851852</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4867404870762695</v>
+        <v>0.217604079246291</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.01634104177355766</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.7120598689052217</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.486740391423136</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.01153762266039848</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.7120598689052217</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4867407421512923</v>
+        <v>0.2176043343213138</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.009340982884168625</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.7120598689052218</v>
+        <v>0.3</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4867404950473639</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.006123397499322891</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.16</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4867404551918916</v>
+        <v>0.2176040473619131</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.01014304533600807</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.6428995442101445</v>
+        <v>0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.486740391423136</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.003997143357992172</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4867404631629861</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.0019269660115242</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.486740391423136</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.01938873901963234</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4867404950473639</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01438218727707863</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5120598689052216</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4867405907004976</v>
+        <v>0.2176041828705191</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.006430581212043762</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4867405269317417</v>
+        <v>0.2176041191017632</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.0009026937186717987</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4867404870762695</v>
+        <v>0.217604079246291</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.01175552234053612</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4867404631629861</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.01053851097822189</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.486740216059058</v>
+        <v>0.2176038082290795</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.007539946585893631</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4867401363481132</v>
+        <v>0.2176037285181347</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01292824372649193</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4867401841746799</v>
+        <v>0.2176037763447014</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002632979303598404</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.486740303741097</v>
+        <v>0.2176038959111185</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.005537521094083786</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5120598689052216</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4867402877989081</v>
+        <v>0.2176038799689296</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.0009631924331188202</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.486740303741097</v>
+        <v>0.2176038959111185</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.009266998618841171</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4867402877989081</v>
+        <v>0.2176038799689296</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.002250742167234421</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4867403435965693</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.002271208912134171</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4867403435965693</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01297556236386299</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4867403435965693</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.000462409108877182</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4867404950473639</v>
+        <v>0.2176040872173854</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.00337349995970726</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4867407102669145</v>
+        <v>0.217604302436936</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.005917895585298538</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4867406225848754</v>
+        <v>0.2176042147548969</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.01117095723748207</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4867405747583087</v>
+        <v>0.2176041669283302</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.008025851100683212</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4867406225848754</v>
+        <v>0.2176042147548969</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.002396054565906525</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4867404392497027</v>
+        <v>0.2176040314197242</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.002944283187389374</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4867404472207972</v>
+        <v>0.2176040393908187</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.01206448301672935</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4867404551918916</v>
+        <v>0.2176040473619131</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0002128668129444122</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4867404631629861</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.00725618377327919</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4867404631629861</v>
+        <v>0.2176040553330076</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.006754707545042038</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4867405030184584</v>
+        <v>0.2176040951884799</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.001997444778680801</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4867405667872142</v>
+        <v>0.2176041589572358</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.00340178981423378</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4867406783825367</v>
+        <v>0.2176042705525581</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.004072126001119614</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4867407262091034</v>
+        <v>0.2176043183791249</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.002153929322957993</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4867406863536311</v>
+        <v>0.2176042785236526</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.007150653749704361</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.486740614613781</v>
+        <v>0.2176042067838025</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.008737776428461075</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4867407341801978</v>
+        <v>0.2176043263502193</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01808375492691994</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4867405747583087</v>
+        <v>0.2176041669283302</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.009125147014856339</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4867403435965693</v>
+        <v>0.2176039357665908</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.0004203468561172485</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.03458016234753856</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4867402957700026</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.00439099594950676</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.8428995442101446</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4867403276543804</v>
+        <v>0.2176039198244019</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.003176357597112656</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.486740391423136</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.008795749396085739</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.5120598689052216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.486740391423136</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.004704587161540985</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.389539575462905</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4867403117121915</v>
+        <v>0.2176039038822129</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.007490918040275574</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7120598689052218</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4867401921457744</v>
+        <v>0.2176037843157959</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.01566333696246147</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.03458016234753856</v>
+        <v>0.3</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4867401522903021</v>
+        <v>0.2176037444603236</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.01054667308926582</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8428995442101446</v>
+        <v>0.3</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4867402957700026</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.0006436742842197418</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.3</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4867404312786083</v>
+        <v>0.2176040234486298</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.006452754139900208</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5120598689052216</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4867404153364194</v>
+        <v>0.2176040075064408</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003247674554586411</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.486740391423136</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.008094571530818939</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.389539575462905</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4867403515676637</v>
+        <v>0.2176039437376852</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.01874670386314392</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7120598689052218</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4867402479434358</v>
+        <v>0.2176038401134573</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.0001109205186367035</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7120598689052217</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4867401283770187</v>
+        <v>0.2176037205470402</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.005716890096664429</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.1654198376524615</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4867402479434358</v>
+        <v>0.2176038401134573</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.007018294185400009</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.5120598689052216</v>
+        <v>0.3</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4867402957700026</v>
+        <v>0.217603887940024</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.009206544607877731</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.1654198376524615</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.486740391423136</v>
+        <v>0.2176039835931575</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.0002536997199058533</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5120598689052216</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4867402718567191</v>
+        <v>0.2176038640267406</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.007464222609996796</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.17332001562638</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4867402798278136</v>
+        <v>0.2176038719978351</v>
       </c>
     </row>
   </sheetData>
